--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-dwh-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-dwh-medium.xlsx
@@ -463,13 +463,13 @@
         <v>Additive: Cộng tổng được qua mọi chiều; Semi-additive: Chỉ cộng được qua một số chiều (như thời gian không cộng được); Non-additive: Không thể cộng tổng (chỉ dùng tỷ lệ) — khả năng cộng gộp số liệu</v>
       </c>
       <c r="G2" t="str">
+        <v>Additive lưu trong database; Semi-additive lưu trên file Excel; Non-additive lưu dạng text thô — hình thức lưu trữ</v>
+      </c>
+      <c r="H2" t="str">
         <v>Additive chỉ dùng cho số dương; Semi-additive dùng cho số âm; Non-additive chỉ dùng cho số thập phân — kiểu số học</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>Additive do DA tự tính; Semi-additive do hệ thống tự tính; Non-additive do PO nhập thủ công — chủ thể tính toán</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Additive lưu trong database; Semi-additive lưu trên file Excel; Non-additive lưu dạng text thô — hình thức lưu trữ</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -492,19 +492,19 @@
         <v>Data Lake lưu trữ tất cả các dạng dữ liệu (cấu trúc, bán cấu trúc, phi cấu trúc) ở định dạng thô với chi phí rẻ. Schema chỉ được định nghĩa khi dữ liệu được đọc ra để sử dụng (Schema-on-read).</v>
       </c>
       <c r="F3" t="str">
+        <v>Data Lake bắt buộc phải sử dụng ngôn ngữ SQL để truy xuất dữ liệu chứ không hỗ trợ Python — giới hạn ngôn ngữ truy vấn</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Data Lake chỉ dùng để lưu trữ dữ liệu lịch sử của các dự án đã thất bại — lưu trữ dự án cũ</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Data Lake chỉ chạy được trên môi trường điện toán đám mây Microsoft Azure — giới hạn môi trường Cloud</v>
+      </c>
+      <c r="I3" t="str">
         <v>Data Lake lưu trữ dữ liệu thô chưa cấu trúc (Schema-on-read); Data Warehouse lưu trữ dữ liệu đã cấu trúc và làm sạch (Schema-on-write) — thô linh hoạt vs cấu trúc chuẩn hóa</v>
       </c>
-      <c r="G3" t="str">
-        <v>Data Lake chỉ chạy được trên môi trường điện toán đám mây Microsoft Azure — giới hạn môi trường Cloud</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Data Lake bắt buộc phải sử dụng ngôn ngữ SQL để truy xuất dữ liệu chứ không hỗ trợ Python — giới hạn ngôn ngữ truy vấn</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Data Lake chỉ dùng để lưu trữ dữ liệu lịch sử của các dự án đã thất bại — lưu trữ dự án cũ</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>SCD Type 2 bảo toàn lịch sử đầy đủ. Khi có thay đổi, nó đóng bản ghi cũ (set End_Date = hiện tại, Is_Active = 0) và tạo một bản ghi mới (Start_Date = hiện tại, End_Date = NULL, Is_Active = 1).</v>
       </c>
       <c r="F4" t="str">
+        <v>Tự động xóa hàng dữ liệu cũ và di chuyển nó sang một file lưu trữ dạng CSV dự phòng — chuyển sang file CSV</v>
+      </c>
+      <c r="G4" t="str">
         <v>Tạo một hàng mới (New Row) trong bảng chiều với khóa chính mới, kèm trường thời hạn hiệu lực (Start_Date, End_Date, Is_Active) — tạo hàng mới lưu lịch sử</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Ghi đè trực tiếp (Overwrite) dữ liệu mới lên dữ liệu cũ, làm mất hoàn toàn thông tin lịch sử trước đó — ghi đè mất lịch sử</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>Tạo thêm một cột mới (New Column) trong cùng một hàng để lưu giá trị cũ ngay cạnh giá trị mới — tạo cột lưu lịch sử</v>
       </c>
-      <c r="I4" t="str">
-        <v>Tự động xóa hàng dữ liệu cũ và di chuyển nó sang một file lưu trữ dạng CSV dự phòng — chuyển sang file CSV</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -559,10 +559,10 @@
         <v>Áp dụng cơ chế nạp dữ liệu tăng trưởng (Incremental Load / Delta Load) bằng cách chỉ trích xuất và biến đổi dữ liệu thay đổi kể từ lần chạy cuối cùng — nạp dữ liệu tăng trưởng</v>
       </c>
       <c r="G5" t="str">
+        <v>Tắt toàn bộ các ràng buộc khóa ngoại và khóa chính trong kho dữ liệu để nạp dữ liệu nhanh hơn — tắt ràng buộc dữ liệu nguy hiểm</v>
+      </c>
+      <c r="H5" t="str">
         <v>Chạy lại toàn bộ dữ liệu từ đầu dự án (Full Load) hàng đêm để đảm bảo tuyệt đối không có sai sót xảy ra — Full Load hàng đêm nặng nề</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Tắt toàn bộ các ràng buộc khóa ngoại và khóa chính trong kho dữ liệu để nạp dữ liệu nhanh hơn — tắt ràng buộc dữ liệu nguy hiểm</v>
       </c>
       <c r="I5" t="str">
         <v>Yêu cầu lập trình viên chia nhỏ dữ liệu thành các tệp tin Excel dung lượng dưới 10MB rồi tải lên bằng tay — thủ công chia nhỏ</v>
@@ -588,19 +588,19 @@
         <v>Conformed Dimension là bảng chiều duy nhất được thiết kế để dùng chung cho nhiều Data Marts/Fact Tables. Nhờ đó, khi ban giám đốc so sánh dữ liệu doanh thu (Sales Fact) và dữ liệu tồn kho (Inventory Fact) theo chiều thời gian (Date Dimension) hoặc chiều sản phẩm (Product Dimension) sẽ luôn khớp nhau.</v>
       </c>
       <c r="F6" t="str">
+        <v>Đảm bảo rằng dữ liệu trong Fact Table không bao giờ được phép chứa các giá trị số âm — ràng buộc số dương</v>
+      </c>
+      <c r="G6" t="str">
         <v>Cho phép nhiều Fact Tables khác nhau trong doanh nghiệp (như Sales, Inventory) sử dụng chung một bảng chiều chuẩn duy nhất (như Date, Customer) để đảm bảo tính nhất quán của báo cáo — đồng bộ hóa báo cáo đa chiều</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Giúp tự động chuyển dịch toàn bộ dữ liệu chuỗi văn bản sang ngôn ngữ tiếng Anh — tự động dịch thuật dữ liệu</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>Giúp tối ưu hóa tốc độ tải trang của các dashboard PowerBI lên nhanh gấp 3 lần — tăng tốc dashboard</v>
       </c>
-      <c r="I6" t="str">
-        <v>Đảm bảo rằng dữ liệu trong Fact Table không bao giờ được phép chứa các giá trị số âm — ràng buộc số dương</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Staging Area giúp tách biệt quá trình trích xuất và biến đổi. Dữ liệu được gom nhanh chóng từ các nguồn OLTP vào Staging (đọc nhanh), sau đó các xử lý biến đổi nặng (Transform) sẽ chạy trên Staging để tránh làm chậm hệ thống đang vận hành trực tiếp của khách hàng.</v>
       </c>
       <c r="F7" t="str">
+        <v>Là phòng họp trực tiếp của các thành viên trong đội ngũ phân tích dữ liệu hàng ngày — phòng họp dự án</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Là hệ thống máy chủ phụ dùng để chạy thử nghiệm các kịch bản kiểm thử bảo mật — máy chủ kiểm thử</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Là nơi chứa các bản vẽ giao diện nháp phục vụ cho việc thiết kế báo cáo trực quan sau này — vùng lưu trữ bản vẽ</v>
+      </c>
+      <c r="I7" t="str">
         <v>Là vùng lưu trữ trung gian chứa dữ liệu thô trích xuất từ nguồn trước khi thực hiện các phép biến đổi phức tạp, tránh gây ảnh hưởng hiệu năng đến hệ thống nguồn OLTP — vùng đệm an toàn</v>
       </c>
-      <c r="G7" t="str">
-        <v>Là nơi chứa các bản vẽ giao diện nháp phục vụ cho việc thiết kế báo cáo trực quan sau này — vùng lưu trữ bản vẽ</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Là phòng họp trực tiếp của các thành viên trong đội ngũ phân tích dữ liệu hàng ngày — phòng họp dự án</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Là hệ thống máy chủ phụ dùng để chạy thử nghiệm các kịch bản kiểm thử bảo mật — máy chủ kiểm thử</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -655,13 +655,13 @@
         <v>Append: Chỉ chèn thêm dữ liệu mới vào cuối bảng; Upsert: Kiểm tra nếu bản ghi đã tồn tại thì cập nhật (Update), nếu chưa tồn tại thì chèn mới (Insert) — chèn thêm vs cập nhật chèn</v>
       </c>
       <c r="G8" t="str">
-        <v>Append chỉ dùng cho bảng chiều; còn Upsert chỉ dùng cho bảng sự kiện — giới hạn phân loại bảng</v>
+        <v>Append bắt buộc phải chạy thủ công bằng tay; còn Upsert luôn chạy tự động qua API — cơ chế kích hoạt</v>
       </c>
       <c r="H8" t="str">
         <v>Append tự động mã hóa dữ liệu; còn Upsert tự động nén kích thước tệp tin nạp — cơ chế lưu trữ kỹ thuật</v>
       </c>
       <c r="I8" t="str">
-        <v>Append bắt buộc phải chạy thủ công bằng tay; còn Upsert luôn chạy tự động qua API — cơ chế kích hoạt</v>
+        <v>Append chỉ dùng cho bảng chiều; còn Upsert chỉ dùng cho bảng sự kiện — giới hạn phân loại bảng</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -684,19 +684,19 @@
         <v>Natural Key (như mã nhân viên, số CCCD) có thể bị thay đổi ở hệ thống nguồn hoặc trùng lặp khi tích hợp nhiều nguồn dữ liệu. Surrogate Key (khóa thay thế vô nghĩa, kiểu int/bigint) đảm bảo tính duy nhất, độc lập với nguồn và giúp câu lệnh JOIN chạy nhanh hơn nhiều so với JOIN qua chuỗi.</v>
       </c>
       <c r="F9" t="str">
+        <v>Vì hệ quản trị cơ sở dữ liệu kho dữ liệu không hỗ trợ lưu khóa chính kiểu chuỗi văn bản — giới hạn kỹ thuật CSDL</v>
+      </c>
+      <c r="G9" t="str">
         <v>Để tránh phụ thuộc vào sự thay đổi mã của hệ thống nguồn, đồng thời tối ưu hóa tốc độ JOIN bảng do khóa thay thế là kiểu số nguyên gọn nhẹ — độc lập nguồn và tối ưu JOIN</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Để khách hàng dễ đọc hiểu và nhớ số khóa chính này khi truy xuất báo cáo — dễ nhớ khóa</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>Để hệ thống tự động mã hóa dữ liệu thông tin nhạy cảm của khách hàng — bảo mật thông tin</v>
       </c>
-      <c r="I9" t="str">
-        <v>Vì hệ quản trị cơ sở dữ liệu kho dữ liệu không hỗ trợ lưu khóa chính kiểu chuỗi văn bản — giới hạn kỹ thuật CSDL</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Degenerate Dimension là các thuộc tính định danh (như Invoice Number, Order ID) không có thuộc tính mô tả nào đi kèm nên không cần tạo bảng chiều riêng. Chúng được đặt thẳng trong Fact Table làm khóa tham chiếu giao dịch.</v>
       </c>
       <c r="F10" t="str">
+        <v>Một cột dữ liệu số tự động giảm giá trị đi 1 đơn vị sau mỗi ngày làm việc — giảm giá trị</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Một bảng chiều chỉ chứa đúng 1 dòng dữ liệu duy nhất dùng để làm mẫu — bảng chiều mẫu</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Một bảng chiều đã bị lỗi cấu trúc dữ liệu và không thể sử dụng để JOIN được nữa — bảng chiều lỗi</v>
+      </c>
+      <c r="I10" t="str">
         <v>Một thuộc tính chiều (như số hóa đơn, số giao dịch) được lưu trực tiếp trong Fact Table mà không cần liên kết với bảng chiều riêng biệt — chiều lưu trực tiếp</v>
       </c>
-      <c r="G10" t="str">
-        <v>Một bảng chiều đã bị lỗi cấu trúc dữ liệu và không thể sử dụng để JOIN được nữa — bảng chiều lỗi</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Một bảng chiều chỉ chứa đúng 1 dòng dữ liệu duy nhất dùng để làm mẫu — bảng chiều mẫu</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Một cột dữ liệu số tự động giảm giá trị đi 1 đơn vị sau mỗi ngày làm việc — giảm giá trị</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -751,13 +751,13 @@
         <v>Đồng bộ hóa toàn bộ các trường ngày giờ về một múi giờ chuẩn duy nhất (thường là UTC) trước khi nạp vào kho dữ liệu — chuẩn hóa múi giờ UTC</v>
       </c>
       <c r="G11" t="str">
-        <v>Giữ nguyên giờ gốc của từng chi nhánh và ghi thêm tên múi giờ dạng text bên cạnh — giữ nguyên ghi chú múi giờ</v>
+        <v>Xóa bỏ toàn bộ phần giờ, phút, giây và chỉ lưu trữ thông tin ngày, tháng, năm — loại bỏ thông tin chi tiết</v>
       </c>
       <c r="H11" t="str">
         <v>Tự động cộng thêm 7 tiếng vào tất cả các trường thời gian không phân biệt nguồn — cộng giờ cố định sai lệch</v>
       </c>
       <c r="I11" t="str">
-        <v>Xóa bỏ toàn bộ phần giờ, phút, giây và chỉ lưu trữ thông tin ngày, tháng, năm — loại bỏ thông tin chi tiết</v>
+        <v>Giữ nguyên giờ gốc của từng chi nhánh và ghi thêm tên múi giờ dạng text bên cạnh — giữ nguyên ghi chú múi giờ</v>
       </c>
       <c r="J11">
         <v>1</v>
